--- a/outputs/问题五计算结果/问题五计算结果.xlsx
+++ b/outputs/问题五计算结果/问题五计算结果.xlsx
@@ -9,20 +9,28 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景电网影响指标" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="连续调节影响比较" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="多园区聚合影响" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平均净交换曲线" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化证据" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="政策建议映射" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一致性校验" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="五档产量稳健性" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="多园区聚合影响" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="极值对应场景" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平均净交换曲线" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="电力系统影响汇总" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化证据" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文献与政策依据" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="政策建议映射" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一致性校验" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'场景电网影响指标'!$A$1:$L$241</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'连续调节影响比较'!$A$1:$Y$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'多园区聚合影响'!$A$1:$L$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'平均净交换曲线'!$A$1:$C$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'量化证据'!$A$1:$D$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'政策建议映射'!$A$1:$D$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'一致性校验'!$A$1:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五档产量稳健性'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'多园区聚合影响'!$A$1:$L$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'极值对应场景'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'平均净交换曲线'!$A$1:$C$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'电力系统影响汇总'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'量化证据'!$A$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'文献与政策依据'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'政策建议映射'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'一致性校验'!$A$1:$D$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10607,6 +10615,593 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>政策编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>政策建议</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>本题量化依据</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>文献政策依据</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>实施逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>完善绿电直连计量、认证与考核机制，统一自发自用和上网比例口径</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>E1、E2</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>避免指标强相关造成重复考核，并真实反映时序交换</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>将最大购电、最大反送、峰谷差和爬坡率纳入接入审查并设置交换功率边界</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>E1、E2、E9</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>把接入评价从年电量扩展至功率与时序风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>建立需求响应和辅助服务补偿，按实际削峰、填谷及爬坡改善量结算</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>E3、E4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>L2、L6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>使柔性制氢制氨负荷的正外部性获得市场回报</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>储能支持由固定容量补贴转向弃电削减、失供避免和调峰绩效补贴</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>L1、L4、L5</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>避免无效堆砌容量，提高财政资金效率</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>建立公平的电网容量和系统运行成本分担机制，并允许辅助服务收益抵扣</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>E8、E9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>L1、L2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>回收备用支撑成本，同时避免重复收费</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>实行并网型、弱并网型和自治型分类管理，不把完全离网作为普遍要求</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>E5、E6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>L1、L4、L5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>兼顾新能源消纳、园区经济性和供电可靠性</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>建立功率预测报送、可观可测可调可控和保护协调技术标准</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>E1、E2、E9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>L1、L5</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>提升大规模接入后的运行可控性</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>检验项目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>计算值</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>目标或容许上限</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>问题二逐时结果行数</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2880</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>问题三逐时结果行数</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2880</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>问题二场景产量组合数</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>问题三场景产量组合数</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>问题二最大功率平衡残差(MW)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>问题二购售电互斥残差(MW^2)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>问题三最大功率平衡残差(MW)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>问题三购售电互斥残差(MW^2)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>36 t/day场景数</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>多园区线性尺度最大残差(MW)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1e-09</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>量化证据条数</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>五档产量稳健性行数</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>极值来源记录数</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>国内外文献及政策来源数</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>正负影响类型数</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>政策双重依据完整性</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>渗透率数值指标列数</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -20262,6 +20857,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日氨产量(t/day)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>场景数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>购电平均变化(MWh)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>购电减少场景数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>售电平均变化(MWh)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>售电减少场景数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>峰谷差平均变化(MW)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>峰谷差减少场景数</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>最大爬坡平均变化(MW/h)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>爬坡减少场景数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2.368475785867e-15</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>2.664535259100376e-15</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-1.480297366166875e-16</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>2.960594732333751e-16</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>-26.00589397149841</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>-19.78995</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>-7.686066677226581</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>-14.44382790017101</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>-42.59479067656187</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>-34.76618029623162</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>-7.308047035546572</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>-7.408846653899677</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>-59.57746483378641</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>-45.42234499168086</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>-14.49956668225929</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>-14.79622553634529</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>-49.43488375364709</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>-39.33071703585824</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>-6.689983410021987</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>-5.786450039046589</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -20667,7 +21501,210 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>代表日氨产量(t/day)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>极值指标</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>极值</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>对应场景</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>风电场景</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>光伏场景</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>口径说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>最大购电功率</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>39.78820000000001</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>风电1-光伏1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>各指标分别取极值，极值不要求来自同一场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>最大反送功率</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>65.46799999999999</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>风电5-光伏1</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>各指标分别取极值，极值不要求来自同一场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>最大交换峰谷差</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>98.56179999999999</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>风电5-光伏1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>各指标分别取极值，极值不要求来自同一场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>最大爬坡功率</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>57.006</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>MW/h</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>风电1-光伏2</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>各指标分别取极值，极值不要求来自同一场景</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21328,7 +22365,318 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>影响类型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>影响编号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>影响</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>作用机理</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>本题量化依据</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>文献政策依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>正面影响</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>促进新能源就地消纳</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>园区内部消纳风光电量，降低部分余电外送需求</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>E1、E2、E4</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>L1、L4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>正面影响</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>提供柔性负荷与调峰能力</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>连续调节将制氢制氨负荷迁移至风光富余或低价时段</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>E3、E4</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L2、L3、L5、L6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>正面影响</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>缓解部分远距离输电需求</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>绿电在园区就近转化为氢氨产品，可减少部分新能源跨区输送</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>E1、E2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>L1、L4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>负面影响</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>同步购电峰和爬坡压力</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>多园区运行相关性高时，购电峰与爬坡功率按接入规模放大</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>E3、E9</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>L1、L2、L6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>负面影响</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>集中反送与反向潮流压力</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>富余风光集中上网可能形成较大的反送功率边界</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>E1、E9</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>负面影响</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>备用与调节需求增加</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>风光预测误差和负荷调节误差需要公共电网提供备用支撑</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>E3、E8、E9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>L1、L2、L5、L6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>负面影响</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>电能质量与保护协调风险</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>大规模电力电子设备和双向潮流提高无功、电能质量及保护配合要求</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>E9（仅边界功率）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>负面影响</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>系统成本与责任分担问题</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>园区依赖电网备用却可能未完全承担容量和系统运行成本</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>E8、E9</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21549,7 +22897,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>20个等效园区同步上界最大购电/反送为795.76/1309.36 MW，多样化期望为693.19/378.35 MW</t>
+          <t>20个等效园区同步上界最大购电/反送为795.76/1309.36 MW，分别来自风电1-光伏1/风电5-光伏1；多样化期望为693.19/378.35 MW</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -21569,440 +22917,249 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>政策编号</t>
+          <t>文献编号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>政策建议</t>
+          <t>类型</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>量化依据</t>
+          <t>作者或机构</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>实施逻辑</t>
+          <t>题名</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>与本题相关结论</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>链接</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>完善绿电直连计量、认证与考核机制，统一自发自用和上网比例口径</t>
+          <t>政策文件</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>E1、E2</t>
+          <t>国家发展改革委、国家能源局</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>避免指标强相关造成重复考核，并真实反映时序交换</t>
+          <t>关于有序推动绿电直连发展有关事项的通知（发改能源〔2025〕650号）</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>要求源荷匹配、交换功率不超过申报容量，鼓励储能和负荷柔性，并落实可观可测可调可控、电能质量和费用责任。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nea.gov.cn/20250530/2d67a6e49c044f2eacabe1fddf48d20f/c.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>将最大购电、最大反送、峰谷差和爬坡率纳入接入审查并设置交换功率边界</t>
+          <t>国内研究</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>E1、E2、E9</t>
+          <t>孔令国等</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>把接入评价从年电量扩展至功率与时序风险</t>
+          <t>基于功率偏差分摊的源氢氨多元耦合系统参与电网调峰优化调度</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>源氢氨系统参与调峰后可降低深度调峰量与净负荷方差，支持按实际调峰绩效给予辅助服务补偿。</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://dgjsxb.ces-transaction.com/CN/10.19595/j.cnki.1000-6753.tces.241938</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>建立需求响应和辅助服务补偿，按实际削峰、填谷及爬坡改善量结算</t>
+          <t>国内研究</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>E3、E4</t>
+          <t>潘禹等</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>使柔性制氢制氨负荷的正外部性获得市场回报</t>
+          <t>含混合电解槽的绿电-绿氢系统能量管理策略研究</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>混合电解槽及其能量管理可利用不同设备效率与动态特性提升可再生能源适应能力。</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tynxb.org.cn/CN/10.19912/j.0254-0096.tynxb.2023-1278</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>储能支持由固定容量补贴转向弃电削减、失供避免和调峰绩效补贴</t>
+          <t>国外研究</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>Armijo and Philibert</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>避免无效堆砌容量，提高财政资金效率</t>
+          <t>Flexible production of green hydrogen and ammonia from variable solar and wind energy</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>风光互补和生产柔性有助于降低可再生能源时序波动及其成本。</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S0360319919342089</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>建立公平的电网容量和系统运行成本分担机制，并允许辅助服务收益抵扣</t>
+          <t>国外研究</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>E8、E9</t>
+          <t>Salmon and Bañares-Alcántara</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>回收备用支撑成本，同时避免重复收费</t>
+          <t>Impact of process flexibility and imperfect forecasting on the operation and design of Haber-Bosch green ammonia</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>基于LP与MPC说明合成氨过程柔性和预测信息共同影响离网绿氨系统的稳健运行与设计。</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://pubs.rsc.org/doi/d3su00067b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>实行并网型、弱并网型和自治型分类管理，不把完全离网作为普遍要求</t>
+          <t>国外研究</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>E5、E6</t>
+          <t>Göke et al.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>兼顾新能源消纳、园区经济性和供电可靠性</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>建立功率预测报送、可观可测可调可控和保护协调技术标准</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>E1、E2、E9</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>提升大规模接入后的运行可控性</t>
+          <t>How flexible electrification can integrate fluctuating renewables</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>灵活电气化尤其是柔性电解槽可降低剩余峰值负荷、剩余需求和过剩发电。</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S0360544223012264</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D8"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>检验项目</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>计算值</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>目标或容许上限</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>结论</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>问题二逐时结果行数</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>2880</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>问题三逐时结果行数</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>2880</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>问题二场景产量组合数</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>问题三场景产量组合数</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>问题二最大功率平衡残差(MW)</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>7.105427357601002e-15</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>问题二购售电互斥残差(MW^2)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>问题三最大功率平衡残差(MW)</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1.4210854715202e-14</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>问题三购售电互斥残差(MW^2)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>36 t/day场景数</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>多园区线性尺度最大残差(MW)</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>1e-09</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>量化证据条数</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D12"/>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>